--- a/output/北塩原村_作業方針_20261011.xlsx
+++ b/output/北塩原村_作業方針_20261011.xlsx
@@ -554,7 +554,7 @@
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>1. 優先A（本文修正）10件は、いずれも既に正本へ反映している。総括は当方の反映後の正本を見ていないため未了として挙げているが、「継続入所者の解釈」は書換４で直して告示の定義を明記し（Ｍ-23で照会）、意思決定支援第2版は移植８で全面改稿し、共生型サービスはＷ-11を書き直している。01シートで、各項目の文字列が正本の現物にあることを生成のたびに確かめている。</t>
+          <t>1. 優先A（本文修正）10件は、いずれも既に正本へ反映している。総括は当方の反映後の正本を見ていないため未了として挙げているが、「継続入所者の解釈」は書換４で直して告示の定義を明記し（Ｍ-109で照会）、意思決定支援第2版は移植８で全面改稿し、共生型サービスはＷ-11を書き直している。01シートで、各項目の文字列が正本の現物にあることを生成のたびに確かめている。</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>第5章1（3）居住系サービス。告示の定義を書き、生活介護及び就労継続支援Ｂ型は現に利用している方を除かないことを明記した（書換４）。照会Ｍ-23</t>
+          <t>第5章1（3）居住系サービス。告示の定義を書き、生活介護及び就労継続支援Ｂ型は現に利用している方を除かないことを明記した（書換４）。照会Ｍ-109</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">

--- a/output/北塩原村_作業方針_20261011.xlsx
+++ b/output/北塩原村_作業方針_20261011.xlsx
@@ -1683,7 +1683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1961,12 +1961,34 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>概要版が4頁から6頁に増えたため、印刷の折り方と部数を村と再確認する</t>
+          <t>概要版が4頁から7頁に増えたため（令和8年10月10日に6頁、同月14日に案Ｃの反映で7頁）、印刷の折り方と部数を村と再確認する。体裁（色だけで区別しないこと、グレースケール、字の大きさ）は他メンバーに確認している（Ｓ-34）</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
           <t>次の打合せ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>当方の環境でできない</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>正本の目次フィールドの更新（章題の変更を含む）</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>令和8年10月14日に第3章の章題を改めた（案Ｃ）。目次は Word の目次フィールドであり、更新しないと古い章題が目次に残る。他メンバーに依頼した（Ｓ-33）。工程上の期限は令和9年2月25日（初校2月26日の前日）</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>他メンバーへ依頼</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_作業方針_20261011.xlsx
+++ b/output/北塩原村_作業方針_20261011.xlsx
@@ -1961,7 +1961,7 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>概要版が4頁から7頁に増えたため（令和8年10月10日に6頁、同月14日に案Ｃの反映で7頁）、印刷の折り方と部数を村と再確認する。体裁（色だけで区別しないこと、グレースケール、字の大きさ）は他メンバーに確認している（Ｓ-34）</t>
+          <t>概要版が4頁から8頁に増えたため（令和8年10月10日に6頁、同月14日に案Ｃの反映で7頁、同日に本文を前回計画と同じ10ポイントにして8頁）、印刷の折り方と部数を村と再確認する。あわせて、前回計画の評価（2頁）とアンケート結果報告（2頁）の概要版を作成した。体裁は前回計画の概要版を実測して揃えた（書体ＵＤデジタル教科書体・本文10ポイント・基調色 緑）。残るのはグラフの凡例をモノクロ印刷で区別できるようにすること（模様又は線の種類で分ける。Ｓ-34）</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
